--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:42</t>
+    <t xml:space="preserve">2026-09-10 00:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:50</t>
+    <t xml:space="preserve">2026-09-18 10:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:59</t>
+    <t xml:space="preserve">2026-09-23 14:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:20</t>
+    <t xml:space="preserve">2026-10-02 15:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:27</t>
+    <t xml:space="preserve">2026-10-05 14:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -662,7 +662,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>72</v>
+        <v>72.01</v>
       </c>
     </row>
     <row r="8">
